--- a/hall/resources/sample/WealthRouletteReward.xlsx
+++ b/hall/resources/sample/WealthRouletteReward.xlsx
@@ -64,7 +64,7 @@
     <t>item</t>
   </si>
   <si>
-    <t>Weight</t>
+    <t>weight</t>
   </si>
   <si>
     <t>picture</t>

--- a/hall/resources/sample/WealthRouletteReward.xlsx
+++ b/hall/resources/sample/WealthRouletteReward.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="56">
   <si>
     <t>ID</t>
   </si>
@@ -76,7 +76,7 @@
     <t>1990000_2000</t>
   </si>
   <si>
-    <t>itemicon_1022504.png</t>
+    <t>cflp_1.png</t>
   </si>
   <si>
     <t>中奖类型2</t>
@@ -115,6 +115,9 @@
     <t>1990000_100000</t>
   </si>
   <si>
+    <t>cflp_2.png</t>
+  </si>
+  <si>
     <t>中奖类型8</t>
   </si>
   <si>
@@ -155,6 +158,9 @@
   </si>
   <si>
     <t>1990000_1500000</t>
+  </si>
+  <si>
+    <t>cflp_3.png</t>
   </si>
   <si>
     <t>中奖类型15</t>
@@ -1392,7 +1398,7 @@
         <v>0.1</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="N11" s="5"/>
       <c r="O11" s="5"/>
@@ -1402,10 +1408,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D12" s="9">
         <v>103</v>
@@ -1415,7 +1421,7 @@
         <v>0.103</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
@@ -1425,10 +1431,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D13" s="9">
         <v>10</v>
@@ -1438,7 +1444,7 @@
         <v>0.01</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
@@ -1448,10 +1454,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" s="9">
         <v>10</v>
@@ -1461,7 +1467,7 @@
         <v>0.01</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
@@ -1471,10 +1477,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" s="9">
         <v>10</v>
@@ -1484,7 +1490,7 @@
         <v>0.01</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
@@ -1494,10 +1500,10 @@
         <v>12</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" s="9">
         <v>5</v>
@@ -1507,7 +1513,7 @@
         <v>0.005</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
@@ -1517,10 +1523,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" s="9">
         <v>5</v>
@@ -1530,7 +1536,7 @@
         <v>0.005</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
@@ -1540,10 +1546,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D18" s="9">
         <v>5</v>
@@ -1553,7 +1559,7 @@
         <v>0.005</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
@@ -1563,10 +1569,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D19" s="9">
         <v>2</v>
@@ -1576,7 +1582,7 @@
         <v>0.002</v>
       </c>
       <c r="F19" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
@@ -1586,10 +1592,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D20" s="9">
         <v>2</v>
@@ -1599,7 +1605,7 @@
         <v>0.002</v>
       </c>
       <c r="F20" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
@@ -1609,10 +1615,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D21" s="9">
         <v>2</v>
@@ -1622,7 +1628,7 @@
         <v>0.002</v>
       </c>
       <c r="F21" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
@@ -1632,10 +1638,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D22" s="9">
         <v>0.5</v>
@@ -1645,7 +1651,7 @@
         <v>0.0005</v>
       </c>
       <c r="F22" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
@@ -1655,10 +1661,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D23" s="9">
         <v>0.3</v>
@@ -1668,7 +1674,7 @@
         <v>0.0003</v>
       </c>
       <c r="F23" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
@@ -1678,10 +1684,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D24" s="9">
         <v>0.2</v>
@@ -1691,7 +1697,7 @@
         <v>0.0002</v>
       </c>
       <c r="F24" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="O24" s="5"/>
     </row>

--- a/hall/resources/sample/WealthRouletteReward.xlsx
+++ b/hall/resources/sample/WealthRouletteReward.xlsx
@@ -76,7 +76,7 @@
     <t>1990000_2000</t>
   </si>
   <si>
-    <t>cflp_1.png</t>
+    <t>cflp_zjm_icon_2.png</t>
   </si>
   <si>
     <t>中奖类型2</t>
@@ -115,7 +115,7 @@
     <t>1990000_100000</t>
   </si>
   <si>
-    <t>cflp_2.png</t>
+    <t>cflp_zjm_icon_3.png</t>
   </si>
   <si>
     <t>中奖类型8</t>
@@ -160,7 +160,7 @@
     <t>1990000_1500000</t>
   </si>
   <si>
-    <t>cflp_3.png</t>
+    <t>cflp_zjm_icon_4.png</t>
   </si>
   <si>
     <t>中奖类型15</t>

--- a/hall/resources/sample/WealthRouletteReward.xlsx
+++ b/hall/resources/sample/WealthRouletteReward.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="37">
   <si>
     <t>ID</t>
   </si>
@@ -40,7 +40,7 @@
     <t>金币档位</t>
   </si>
   <si>
-    <t>权重（千分比）</t>
+    <t>权重（万分比）</t>
   </si>
   <si>
     <t>#备注</t>
@@ -70,7 +70,7 @@
     <t>picture</t>
   </si>
   <si>
-    <t>中奖类型1</t>
+    <t>金币</t>
   </si>
   <si>
     <t>1990000_2000</t>
@@ -79,121 +79,64 @@
     <t>cflp_zjm_icon_2.png</t>
   </si>
   <si>
-    <t>中奖类型2</t>
-  </si>
-  <si>
     <t>1990000_5000</t>
   </si>
   <si>
-    <t>中奖类型3</t>
-  </si>
-  <si>
     <t>1990000_10000</t>
   </si>
   <si>
-    <t>中奖类型4</t>
-  </si>
-  <si>
     <t>1990000_20000</t>
   </si>
   <si>
-    <t>中奖类型5</t>
-  </si>
-  <si>
     <t>1990000_50000</t>
   </si>
   <si>
-    <t>中奖类型6</t>
-  </si>
-  <si>
     <t>1990000_80000</t>
   </si>
   <si>
-    <t>中奖类型7</t>
-  </si>
-  <si>
     <t>1990000_100000</t>
   </si>
   <si>
     <t>cflp_zjm_icon_3.png</t>
   </si>
   <si>
-    <t>中奖类型8</t>
-  </si>
-  <si>
     <t>1990000_150000</t>
   </si>
   <si>
-    <t>中奖类型9</t>
-  </si>
-  <si>
     <t>1990000_200000</t>
   </si>
   <si>
-    <t>中奖类型10</t>
-  </si>
-  <si>
     <t>1990000_300000</t>
   </si>
   <si>
-    <t>中奖类型11</t>
-  </si>
-  <si>
     <t>1990000_500000</t>
   </si>
   <si>
-    <t>中奖类型12</t>
-  </si>
-  <si>
     <t>1990000_800000</t>
   </si>
   <si>
-    <t>中奖类型13</t>
-  </si>
-  <si>
     <t>1990000_1000000</t>
   </si>
   <si>
-    <t>中奖类型14</t>
-  </si>
-  <si>
     <t>1990000_1500000</t>
   </si>
   <si>
     <t>cflp_zjm_icon_4.png</t>
   </si>
   <si>
-    <t>中奖类型15</t>
-  </si>
-  <si>
     <t>1990000_2000000</t>
   </si>
   <si>
-    <t>中奖类型16</t>
-  </si>
-  <si>
     <t>1990000_2500000</t>
   </si>
   <si>
-    <t>中奖类型17</t>
-  </si>
-  <si>
     <t>1990000_5000000</t>
   </si>
   <si>
-    <t>中奖类型18</t>
-  </si>
-  <si>
     <t>1990000_8000000</t>
   </si>
   <si>
-    <t>中奖类型19</t>
-  </si>
-  <si>
     <t>1990000_10000000</t>
-  </si>
-  <si>
-    <t>中奖类型20</t>
   </si>
   <si>
     <t>1990000_20000000</t>
@@ -843,17 +786,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
@@ -1246,17 +1189,17 @@
       <c r="A5" s="7">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="9">
-        <v>130</v>
-      </c>
-      <c r="E5" s="10">
-        <f>D5/1000</f>
+      <c r="D5" s="8">
+        <v>1300</v>
+      </c>
+      <c r="E5" s="9">
+        <f>D5/10000</f>
         <v>0.13</v>
       </c>
       <c r="F5" t="s">
@@ -1269,17 +1212,17 @@
       <c r="A6" s="7">
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="9">
-        <v>140</v>
-      </c>
-      <c r="E6" s="10">
-        <f>D6/1000</f>
+      <c r="D6" s="8">
+        <v>1400</v>
+      </c>
+      <c r="E6" s="9">
+        <f t="shared" ref="E6:E24" si="0">D6/10000</f>
         <v>0.14</v>
       </c>
       <c r="F6" t="s">
@@ -1292,17 +1235,17 @@
       <c r="A7" s="7">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>18</v>
+      <c r="B7" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="9">
-        <v>150</v>
-      </c>
-      <c r="E7" s="10">
-        <f t="shared" ref="E7:E25" si="0">D7/1000</f>
+        <v>17</v>
+      </c>
+      <c r="D7" s="8">
+        <v>1500</v>
+      </c>
+      <c r="E7" s="9">
+        <f t="shared" si="0"/>
         <v>0.15</v>
       </c>
       <c r="F7" t="s">
@@ -1315,16 +1258,16 @@
       <c r="A8" s="7">
         <v>4</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>20</v>
+      <c r="B8" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="9">
-        <v>120</v>
-      </c>
-      <c r="E8" s="10">
+        <v>18</v>
+      </c>
+      <c r="D8" s="8">
+        <v>1200</v>
+      </c>
+      <c r="E8" s="9">
         <f t="shared" si="0"/>
         <v>0.12</v>
       </c>
@@ -1338,16 +1281,16 @@
       <c r="A9" s="7">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>22</v>
+      <c r="B9" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="9">
-        <v>105</v>
-      </c>
-      <c r="E9" s="10">
+        <v>19</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1050</v>
+      </c>
+      <c r="E9" s="9">
         <f t="shared" si="0"/>
         <v>0.105</v>
       </c>
@@ -1361,16 +1304,16 @@
       <c r="A10" s="7">
         <v>6</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>24</v>
+      <c r="B10" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="9">
-        <v>100</v>
-      </c>
-      <c r="E10" s="10">
+        <v>20</v>
+      </c>
+      <c r="D10" s="8">
+        <v>1000</v>
+      </c>
+      <c r="E10" s="9">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
@@ -1384,21 +1327,21 @@
       <c r="A11" s="7">
         <v>7</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>26</v>
+      <c r="B11" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="9">
-        <v>100</v>
-      </c>
-      <c r="E11" s="10">
+        <v>21</v>
+      </c>
+      <c r="D11" s="8">
+        <v>1000</v>
+      </c>
+      <c r="E11" s="9">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
       <c r="F11" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="N11" s="5"/>
       <c r="O11" s="5"/>
@@ -1407,21 +1350,21 @@
       <c r="A12" s="7">
         <v>8</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>29</v>
+      <c r="B12" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="9">
-        <v>103</v>
-      </c>
-      <c r="E12" s="10">
+        <v>23</v>
+      </c>
+      <c r="D12" s="8">
+        <v>1030</v>
+      </c>
+      <c r="E12" s="9">
         <f t="shared" si="0"/>
         <v>0.103</v>
       </c>
       <c r="F12" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
@@ -1430,21 +1373,21 @@
       <c r="A13" s="7">
         <v>9</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>31</v>
+      <c r="B13" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="9">
-        <v>10</v>
-      </c>
-      <c r="E13" s="10">
+        <v>24</v>
+      </c>
+      <c r="D13" s="8">
+        <v>100</v>
+      </c>
+      <c r="E13" s="9">
         <f t="shared" si="0"/>
         <v>0.01</v>
       </c>
       <c r="F13" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
@@ -1453,21 +1396,21 @@
       <c r="A14" s="7">
         <v>10</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>33</v>
+      <c r="B14" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="9">
-        <v>10</v>
-      </c>
-      <c r="E14" s="10">
+        <v>25</v>
+      </c>
+      <c r="D14" s="8">
+        <v>100</v>
+      </c>
+      <c r="E14" s="9">
         <f t="shared" si="0"/>
         <v>0.01</v>
       </c>
       <c r="F14" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
@@ -1476,21 +1419,21 @@
       <c r="A15" s="7">
         <v>11</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>35</v>
+      <c r="B15" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="9">
-        <v>10</v>
-      </c>
-      <c r="E15" s="10">
+        <v>26</v>
+      </c>
+      <c r="D15" s="8">
+        <v>100</v>
+      </c>
+      <c r="E15" s="9">
         <f t="shared" si="0"/>
         <v>0.01</v>
       </c>
       <c r="F15" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
@@ -1499,21 +1442,21 @@
       <c r="A16" s="7">
         <v>12</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>37</v>
+      <c r="B16" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="9">
-        <v>5</v>
-      </c>
-      <c r="E16" s="10">
+        <v>27</v>
+      </c>
+      <c r="D16" s="8">
+        <v>50</v>
+      </c>
+      <c r="E16" s="9">
         <f t="shared" si="0"/>
         <v>0.005</v>
       </c>
       <c r="F16" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
@@ -1522,21 +1465,21 @@
       <c r="A17" s="7">
         <v>13</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>39</v>
+      <c r="B17" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" s="9">
-        <v>5</v>
-      </c>
-      <c r="E17" s="10">
+        <v>28</v>
+      </c>
+      <c r="D17" s="8">
+        <v>50</v>
+      </c>
+      <c r="E17" s="9">
         <f t="shared" si="0"/>
         <v>0.005</v>
       </c>
       <c r="F17" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
@@ -1545,21 +1488,21 @@
       <c r="A18" s="7">
         <v>14</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>41</v>
+      <c r="B18" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" s="9">
-        <v>5</v>
-      </c>
-      <c r="E18" s="10">
+        <v>29</v>
+      </c>
+      <c r="D18" s="8">
+        <v>50</v>
+      </c>
+      <c r="E18" s="9">
         <f t="shared" si="0"/>
         <v>0.005</v>
       </c>
       <c r="F18" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
@@ -1568,21 +1511,21 @@
       <c r="A19" s="7">
         <v>15</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>44</v>
+      <c r="B19" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="9">
-        <v>2</v>
-      </c>
-      <c r="E19" s="10">
+        <v>31</v>
+      </c>
+      <c r="D19" s="8">
+        <v>20</v>
+      </c>
+      <c r="E19" s="9">
         <f t="shared" si="0"/>
         <v>0.002</v>
       </c>
       <c r="F19" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
@@ -1591,21 +1534,21 @@
       <c r="A20" s="7">
         <v>16</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>46</v>
+      <c r="B20" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" s="9">
-        <v>2</v>
-      </c>
-      <c r="E20" s="10">
+        <v>32</v>
+      </c>
+      <c r="D20" s="8">
+        <v>20</v>
+      </c>
+      <c r="E20" s="9">
         <f t="shared" si="0"/>
         <v>0.002</v>
       </c>
       <c r="F20" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
@@ -1614,21 +1557,21 @@
       <c r="A21" s="7">
         <v>17</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>48</v>
+      <c r="B21" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="9">
-        <v>2</v>
-      </c>
-      <c r="E21" s="10">
+        <v>33</v>
+      </c>
+      <c r="D21" s="8">
+        <v>20</v>
+      </c>
+      <c r="E21" s="9">
         <f t="shared" si="0"/>
         <v>0.002</v>
       </c>
       <c r="F21" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
@@ -1637,21 +1580,21 @@
       <c r="A22" s="7">
         <v>18</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>50</v>
+      <c r="B22" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="E22" s="10">
+        <v>34</v>
+      </c>
+      <c r="D22" s="8">
+        <v>5</v>
+      </c>
+      <c r="E22" s="9">
         <f t="shared" si="0"/>
         <v>0.0005</v>
       </c>
       <c r="F22" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
@@ -1660,21 +1603,21 @@
       <c r="A23" s="7">
         <v>19</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>52</v>
+      <c r="B23" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D23" s="9">
-        <v>0.3</v>
-      </c>
-      <c r="E23" s="10">
+        <v>35</v>
+      </c>
+      <c r="D23" s="8">
+        <v>3</v>
+      </c>
+      <c r="E23" s="9">
         <f t="shared" si="0"/>
         <v>0.0003</v>
       </c>
       <c r="F23" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
@@ -1683,779 +1626,779 @@
       <c r="A24" s="7">
         <v>20</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>54</v>
+      <c r="B24" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24" s="9">
-        <v>0.2</v>
-      </c>
-      <c r="E24" s="10">
+        <v>36</v>
+      </c>
+      <c r="D24" s="8">
+        <v>2</v>
+      </c>
+      <c r="E24" s="9">
         <f t="shared" si="0"/>
         <v>0.0002</v>
       </c>
       <c r="F24" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="O24" s="5"/>
     </row>
     <row r="25" spans="1:15">
-      <c r="A25" s="11"/>
-      <c r="B25" s="8"/>
+      <c r="A25" s="10"/>
+      <c r="B25" s="11"/>
       <c r="C25" s="5"/>
     </row>
     <row r="26" customFormat="1" spans="1:15">
-      <c r="A26" s="11"/>
-      <c r="B26" s="8"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="11"/>
       <c r="C26" s="5"/>
     </row>
     <row r="27" customFormat="1" spans="1:15">
-      <c r="A27" s="11"/>
-      <c r="B27" s="8"/>
+      <c r="A27" s="10"/>
+      <c r="B27" s="11"/>
       <c r="C27" s="5"/>
     </row>
     <row r="28" customFormat="1" spans="1:15">
-      <c r="A28" s="11"/>
-      <c r="B28" s="8"/>
+      <c r="A28" s="10"/>
+      <c r="B28" s="11"/>
       <c r="C28" s="5"/>
     </row>
     <row r="29" customFormat="1" spans="1:15">
-      <c r="A29" s="11"/>
-      <c r="B29" s="8"/>
+      <c r="A29" s="10"/>
+      <c r="B29" s="11"/>
       <c r="C29" s="5"/>
     </row>
     <row r="30" customFormat="1" spans="1:15">
-      <c r="A30" s="11"/>
-      <c r="B30" s="8"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="11"/>
       <c r="C30" s="5"/>
     </row>
     <row r="31" customFormat="1" spans="1:15">
-      <c r="A31" s="11"/>
-      <c r="B31" s="8"/>
+      <c r="A31" s="10"/>
+      <c r="B31" s="11"/>
       <c r="C31" s="5"/>
     </row>
     <row r="32" customFormat="1" spans="1:15">
-      <c r="A32" s="11"/>
-      <c r="B32" s="8"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="11"/>
       <c r="C32" s="5"/>
     </row>
     <row r="33" customFormat="1" spans="1:3">
-      <c r="A33" s="11"/>
-      <c r="B33" s="8"/>
+      <c r="A33" s="10"/>
+      <c r="B33" s="11"/>
       <c r="C33" s="5"/>
     </row>
     <row r="34" customFormat="1" spans="1:3">
-      <c r="A34" s="11"/>
-      <c r="B34" s="8"/>
+      <c r="A34" s="10"/>
+      <c r="B34" s="11"/>
       <c r="C34" s="5"/>
     </row>
     <row r="35" customFormat="1" spans="1:3">
-      <c r="A35" s="11"/>
-      <c r="B35" s="8"/>
+      <c r="A35" s="10"/>
+      <c r="B35" s="11"/>
     </row>
     <row r="36" customFormat="1" spans="1:3">
-      <c r="A36" s="11"/>
-      <c r="B36" s="8"/>
+      <c r="A36" s="10"/>
+      <c r="B36" s="11"/>
     </row>
     <row r="37" customFormat="1" spans="1:3">
-      <c r="A37" s="11"/>
-      <c r="B37" s="8"/>
+      <c r="A37" s="10"/>
+      <c r="B37" s="11"/>
       <c r="C37" s="5"/>
     </row>
     <row r="38" customFormat="1" spans="1:3">
-      <c r="A38" s="11"/>
-      <c r="B38" s="8"/>
+      <c r="A38" s="10"/>
+      <c r="B38" s="11"/>
       <c r="C38" s="5"/>
     </row>
     <row r="39" customFormat="1" spans="1:3">
-      <c r="A39" s="11"/>
-      <c r="B39" s="8"/>
+      <c r="A39" s="10"/>
+      <c r="B39" s="11"/>
       <c r="C39" s="5"/>
     </row>
     <row r="40" customFormat="1" spans="1:3">
-      <c r="A40" s="11"/>
-      <c r="B40" s="8"/>
+      <c r="A40" s="10"/>
+      <c r="B40" s="11"/>
     </row>
     <row r="41" customFormat="1" spans="1:3">
-      <c r="A41" s="11"/>
-      <c r="B41" s="8"/>
+      <c r="A41" s="10"/>
+      <c r="B41" s="11"/>
       <c r="C41" s="5"/>
     </row>
     <row r="42" customFormat="1" spans="1:3">
-      <c r="A42" s="11"/>
-      <c r="B42" s="8"/>
+      <c r="A42" s="10"/>
+      <c r="B42" s="11"/>
     </row>
     <row r="43" customFormat="1" spans="1:3">
-      <c r="A43" s="11"/>
-      <c r="B43" s="8"/>
+      <c r="A43" s="10"/>
+      <c r="B43" s="11"/>
       <c r="C43" s="5"/>
     </row>
     <row r="44" customFormat="1" spans="1:3">
-      <c r="A44" s="11"/>
-      <c r="B44" s="8"/>
+      <c r="A44" s="10"/>
+      <c r="B44" s="11"/>
       <c r="C44" s="5"/>
     </row>
     <row r="45" customFormat="1" spans="1:3">
-      <c r="A45" s="11"/>
-      <c r="B45" s="8"/>
+      <c r="A45" s="10"/>
+      <c r="B45" s="11"/>
       <c r="C45" s="5"/>
     </row>
     <row r="46" customFormat="1" spans="1:3">
-      <c r="A46" s="11"/>
-      <c r="B46" s="8"/>
+      <c r="A46" s="10"/>
+      <c r="B46" s="11"/>
       <c r="C46" s="5"/>
     </row>
     <row r="47" customFormat="1" spans="1:3">
-      <c r="A47" s="11"/>
-      <c r="B47" s="8"/>
+      <c r="A47" s="10"/>
+      <c r="B47" s="11"/>
       <c r="C47" s="5"/>
     </row>
     <row r="48" customFormat="1" spans="1:3">
-      <c r="A48" s="11"/>
-      <c r="B48" s="8"/>
+      <c r="A48" s="10"/>
+      <c r="B48" s="11"/>
       <c r="C48" s="5"/>
     </row>
     <row r="49" customFormat="1" spans="1:3">
-      <c r="A49" s="11"/>
-      <c r="B49" s="8"/>
+      <c r="A49" s="10"/>
+      <c r="B49" s="11"/>
       <c r="C49" s="5"/>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="11"/>
-      <c r="B50" s="8"/>
+      <c r="A50" s="10"/>
+      <c r="B50" s="11"/>
       <c r="C50" s="5"/>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="11"/>
-      <c r="B51" s="8"/>
+      <c r="A51" s="10"/>
+      <c r="B51" s="11"/>
       <c r="C51" s="5"/>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="11"/>
-      <c r="B52" s="8"/>
+      <c r="A52" s="10"/>
+      <c r="B52" s="11"/>
       <c r="C52" s="5"/>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="11"/>
-      <c r="B53" s="8"/>
+      <c r="A53" s="10"/>
+      <c r="B53" s="11"/>
       <c r="C53" s="5"/>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="11"/>
-      <c r="B54" s="8"/>
+      <c r="A54" s="10"/>
+      <c r="B54" s="11"/>
       <c r="C54" s="5"/>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="11"/>
-      <c r="B55" s="8"/>
+      <c r="A55" s="10"/>
+      <c r="B55" s="11"/>
       <c r="C55" s="5"/>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="11"/>
-      <c r="B56" s="8"/>
+      <c r="A56" s="10"/>
+      <c r="B56" s="11"/>
       <c r="C56" s="5"/>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="11"/>
-      <c r="B57" s="8"/>
+      <c r="A57" s="10"/>
+      <c r="B57" s="11"/>
       <c r="C57" s="5"/>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="11"/>
-      <c r="B58" s="8"/>
+      <c r="A58" s="10"/>
+      <c r="B58" s="11"/>
       <c r="C58" s="5"/>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="11"/>
-      <c r="B59" s="8"/>
+      <c r="A59" s="10"/>
+      <c r="B59" s="11"/>
       <c r="C59" s="5"/>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="11"/>
-      <c r="B60" s="8"/>
+      <c r="A60" s="10"/>
+      <c r="B60" s="11"/>
       <c r="C60" s="5"/>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="11"/>
-      <c r="B61" s="8"/>
+      <c r="A61" s="10"/>
+      <c r="B61" s="11"/>
       <c r="C61" s="5"/>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62" s="11"/>
-      <c r="B62" s="8"/>
+      <c r="A62" s="10"/>
+      <c r="B62" s="11"/>
       <c r="C62" s="5"/>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="11"/>
-      <c r="B63" s="8"/>
+      <c r="A63" s="10"/>
+      <c r="B63" s="11"/>
       <c r="C63" s="5"/>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="11"/>
-      <c r="B64" s="8"/>
+      <c r="A64" s="10"/>
+      <c r="B64" s="11"/>
       <c r="C64" s="5"/>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65" s="11"/>
-      <c r="B65" s="8"/>
+      <c r="A65" s="10"/>
+      <c r="B65" s="11"/>
       <c r="C65" s="5"/>
     </row>
     <row r="66" spans="1:3">
-      <c r="A66" s="11"/>
-      <c r="B66" s="8"/>
+      <c r="A66" s="10"/>
+      <c r="B66" s="11"/>
       <c r="C66" s="5"/>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="11"/>
-      <c r="B67" s="8"/>
+      <c r="A67" s="10"/>
+      <c r="B67" s="11"/>
       <c r="C67" s="5"/>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="11"/>
-      <c r="B68" s="8"/>
+      <c r="A68" s="10"/>
+      <c r="B68" s="11"/>
       <c r="C68" s="5"/>
     </row>
     <row r="69" spans="1:3">
-      <c r="A69" s="11"/>
-      <c r="B69" s="8"/>
+      <c r="A69" s="10"/>
+      <c r="B69" s="11"/>
       <c r="C69" s="5"/>
     </row>
     <row r="70" spans="1:3">
-      <c r="A70" s="11"/>
-      <c r="B70" s="8"/>
+      <c r="A70" s="10"/>
+      <c r="B70" s="11"/>
       <c r="C70" s="5"/>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="11"/>
-      <c r="B71" s="8"/>
+      <c r="A71" s="10"/>
+      <c r="B71" s="11"/>
       <c r="C71" s="5"/>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="11"/>
-      <c r="B72" s="8"/>
+      <c r="A72" s="10"/>
+      <c r="B72" s="11"/>
       <c r="C72" s="5"/>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="11"/>
-      <c r="B73" s="8"/>
+      <c r="A73" s="10"/>
+      <c r="B73" s="11"/>
       <c r="C73" s="5"/>
     </row>
     <row r="74" spans="1:3">
-      <c r="A74" s="11"/>
-      <c r="B74" s="8"/>
+      <c r="A74" s="10"/>
+      <c r="B74" s="11"/>
       <c r="C74" s="5"/>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="11"/>
-      <c r="B75" s="8"/>
+      <c r="A75" s="10"/>
+      <c r="B75" s="11"/>
       <c r="C75" s="5"/>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="11"/>
-      <c r="B76" s="8"/>
+      <c r="A76" s="10"/>
+      <c r="B76" s="11"/>
       <c r="C76" s="5"/>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="11"/>
-      <c r="B77" s="8"/>
+      <c r="A77" s="10"/>
+      <c r="B77" s="11"/>
       <c r="C77" s="5"/>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78" s="11"/>
-      <c r="B78" s="8"/>
+      <c r="A78" s="10"/>
+      <c r="B78" s="11"/>
       <c r="C78" s="5"/>
     </row>
     <row r="79" spans="1:3">
-      <c r="A79" s="11"/>
-      <c r="B79" s="8"/>
+      <c r="A79" s="10"/>
+      <c r="B79" s="11"/>
       <c r="C79" s="5"/>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="11"/>
-      <c r="B80" s="8"/>
+      <c r="A80" s="10"/>
+      <c r="B80" s="11"/>
       <c r="C80" s="5"/>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="11"/>
-      <c r="B81" s="8"/>
+      <c r="A81" s="10"/>
+      <c r="B81" s="11"/>
       <c r="C81" s="5"/>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="11"/>
-      <c r="B82" s="8"/>
+      <c r="A82" s="10"/>
+      <c r="B82" s="11"/>
       <c r="C82" s="5"/>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="11"/>
-      <c r="B83" s="8"/>
+      <c r="A83" s="10"/>
+      <c r="B83" s="11"/>
       <c r="C83" s="5"/>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="11"/>
-      <c r="B84" s="8"/>
+      <c r="A84" s="10"/>
+      <c r="B84" s="11"/>
       <c r="C84" s="5"/>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85" s="11"/>
-      <c r="B85" s="8"/>
+      <c r="A85" s="10"/>
+      <c r="B85" s="11"/>
       <c r="C85" s="5"/>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86" s="11"/>
-      <c r="B86" s="8"/>
+      <c r="A86" s="10"/>
+      <c r="B86" s="11"/>
       <c r="C86" s="5"/>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="11"/>
-      <c r="B87" s="8"/>
+      <c r="A87" s="10"/>
+      <c r="B87" s="11"/>
       <c r="C87" s="5"/>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="11"/>
-      <c r="B88" s="8"/>
+      <c r="A88" s="10"/>
+      <c r="B88" s="11"/>
       <c r="C88" s="5"/>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="11"/>
-      <c r="B89" s="8"/>
+      <c r="A89" s="10"/>
+      <c r="B89" s="11"/>
       <c r="C89" s="5"/>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90" s="11"/>
-      <c r="B90" s="8"/>
+      <c r="A90" s="10"/>
+      <c r="B90" s="11"/>
       <c r="C90" s="5"/>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="11"/>
-      <c r="B91" s="8"/>
+      <c r="A91" s="10"/>
+      <c r="B91" s="11"/>
       <c r="C91" s="5"/>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="11"/>
-      <c r="B92" s="8"/>
+      <c r="A92" s="10"/>
+      <c r="B92" s="11"/>
       <c r="C92" s="5"/>
     </row>
     <row r="93" spans="1:3">
-      <c r="A93" s="11"/>
-      <c r="B93" s="8"/>
+      <c r="A93" s="10"/>
+      <c r="B93" s="11"/>
       <c r="C93" s="5"/>
     </row>
     <row r="94" spans="1:3">
-      <c r="A94" s="11"/>
-      <c r="B94" s="8"/>
+      <c r="A94" s="10"/>
+      <c r="B94" s="11"/>
       <c r="C94" s="5"/>
     </row>
     <row r="95" spans="1:3">
-      <c r="A95" s="11"/>
-      <c r="B95" s="8"/>
+      <c r="A95" s="10"/>
+      <c r="B95" s="11"/>
       <c r="C95" s="5"/>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="11"/>
-      <c r="B96" s="8"/>
+      <c r="A96" s="10"/>
+      <c r="B96" s="11"/>
       <c r="C96" s="5"/>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="11"/>
-      <c r="B97" s="8"/>
+      <c r="A97" s="10"/>
+      <c r="B97" s="11"/>
       <c r="C97" s="5"/>
     </row>
     <row r="98" spans="1:3">
-      <c r="A98" s="11"/>
+      <c r="A98" s="10"/>
       <c r="B98" s="12"/>
       <c r="C98" s="5"/>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="11"/>
+      <c r="A99" s="10"/>
       <c r="B99" s="12"/>
       <c r="C99" s="5"/>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="11"/>
+      <c r="A100" s="10"/>
       <c r="B100" s="12"/>
       <c r="C100" s="5"/>
     </row>
     <row r="101" spans="1:3">
-      <c r="A101" s="11"/>
+      <c r="A101" s="10"/>
       <c r="B101" s="12"/>
       <c r="C101" s="5"/>
     </row>
     <row r="102" spans="1:3">
-      <c r="A102" s="11"/>
+      <c r="A102" s="10"/>
       <c r="B102" s="12"/>
       <c r="C102" s="5"/>
     </row>
     <row r="103" spans="1:3">
-      <c r="A103" s="11"/>
+      <c r="A103" s="10"/>
       <c r="B103" s="12"/>
       <c r="C103" s="5"/>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="11"/>
+      <c r="A104" s="10"/>
       <c r="B104" s="12"/>
       <c r="C104" s="5"/>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="11"/>
+      <c r="A105" s="10"/>
       <c r="B105" s="12"/>
       <c r="C105" s="5"/>
     </row>
     <row r="106" spans="1:3">
-      <c r="A106" s="11"/>
+      <c r="A106" s="10"/>
       <c r="B106" s="12"/>
       <c r="C106" s="5"/>
     </row>
     <row r="107" spans="1:3">
-      <c r="A107" s="11"/>
+      <c r="A107" s="10"/>
       <c r="B107" s="12"/>
       <c r="C107" s="5"/>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108" s="11"/>
+      <c r="A108" s="10"/>
       <c r="B108" s="12"/>
       <c r="C108" s="5"/>
     </row>
     <row r="109" spans="1:3">
-      <c r="A109" s="11"/>
+      <c r="A109" s="10"/>
       <c r="B109" s="12"/>
       <c r="C109" s="5"/>
     </row>
     <row r="110" spans="1:3">
-      <c r="A110" s="11"/>
+      <c r="A110" s="10"/>
       <c r="C110" s="5"/>
     </row>
     <row r="111" spans="1:3">
-      <c r="A111" s="11"/>
+      <c r="A111" s="10"/>
       <c r="C111" s="5"/>
     </row>
     <row r="112" spans="1:3">
-      <c r="A112" s="11"/>
+      <c r="A112" s="10"/>
       <c r="C112" s="5"/>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="11"/>
+      <c r="A113" s="10"/>
       <c r="C113" s="5"/>
     </row>
     <row r="114" spans="1:3">
-      <c r="A114" s="11"/>
+      <c r="A114" s="10"/>
       <c r="C114" s="5"/>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" s="11"/>
+      <c r="A115" s="10"/>
       <c r="C115" s="5"/>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" s="11"/>
+      <c r="A116" s="10"/>
       <c r="C116" s="5"/>
     </row>
     <row r="117" spans="1:3">
-      <c r="A117" s="11"/>
+      <c r="A117" s="10"/>
       <c r="C117" s="5"/>
     </row>
     <row r="118" spans="1:3">
-      <c r="A118" s="11"/>
+      <c r="A118" s="10"/>
       <c r="C118" s="5"/>
     </row>
     <row r="119" spans="1:3">
-      <c r="A119" s="11"/>
+      <c r="A119" s="10"/>
       <c r="C119" s="5"/>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="11"/>
+      <c r="A120" s="10"/>
       <c r="C120" s="5"/>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121" s="11"/>
+      <c r="A121" s="10"/>
       <c r="C121" s="5"/>
     </row>
     <row r="122" spans="1:3">
-      <c r="A122" s="11"/>
+      <c r="A122" s="10"/>
       <c r="C122" s="5"/>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123" s="11"/>
+      <c r="A123" s="10"/>
       <c r="C123" s="5"/>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="11"/>
+      <c r="A124" s="10"/>
       <c r="C124" s="5"/>
     </row>
     <row r="125" spans="1:3">
-      <c r="A125" s="11"/>
+      <c r="A125" s="10"/>
       <c r="C125" s="5"/>
     </row>
     <row r="126" spans="1:3">
-      <c r="A126" s="11"/>
+      <c r="A126" s="10"/>
       <c r="C126" s="5"/>
     </row>
     <row r="127" spans="1:3">
-      <c r="A127" s="11"/>
+      <c r="A127" s="10"/>
       <c r="C127" s="5"/>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="11"/>
+      <c r="A128" s="10"/>
       <c r="C128" s="5"/>
     </row>
     <row r="129" spans="1:3">
-      <c r="A129" s="11"/>
+      <c r="A129" s="10"/>
       <c r="C129" s="5"/>
     </row>
     <row r="130" spans="1:3">
-      <c r="A130" s="11"/>
+      <c r="A130" s="10"/>
       <c r="C130" s="5"/>
     </row>
     <row r="131" spans="1:3">
-      <c r="A131" s="11"/>
+      <c r="A131" s="10"/>
       <c r="C131" s="5"/>
     </row>
     <row r="132" spans="1:3">
-      <c r="A132" s="11"/>
+      <c r="A132" s="10"/>
       <c r="C132" s="5"/>
     </row>
     <row r="133" spans="1:3">
-      <c r="A133" s="11"/>
+      <c r="A133" s="10"/>
       <c r="C133" s="5"/>
     </row>
     <row r="134" spans="1:3">
-      <c r="A134" s="11"/>
+      <c r="A134" s="10"/>
       <c r="C134" s="5"/>
     </row>
     <row r="135" spans="1:3">
-      <c r="A135" s="11"/>
+      <c r="A135" s="10"/>
       <c r="C135" s="5"/>
     </row>
     <row r="136" spans="1:3">
-      <c r="A136" s="11"/>
+      <c r="A136" s="10"/>
       <c r="C136" s="5"/>
     </row>
     <row r="137" spans="1:3">
-      <c r="A137" s="11"/>
+      <c r="A137" s="10"/>
       <c r="C137" s="5"/>
     </row>
     <row r="138" spans="1:3">
-      <c r="A138" s="11"/>
+      <c r="A138" s="10"/>
       <c r="C138" s="5"/>
     </row>
     <row r="139" spans="1:3">
-      <c r="A139" s="11"/>
+      <c r="A139" s="10"/>
       <c r="C139" s="5"/>
     </row>
     <row r="140" spans="1:3">
-      <c r="A140" s="11"/>
+      <c r="A140" s="10"/>
       <c r="C140" s="5"/>
     </row>
     <row r="141" spans="1:3">
-      <c r="A141" s="11"/>
+      <c r="A141" s="10"/>
       <c r="C141" s="5"/>
     </row>
     <row r="142" spans="1:3">
-      <c r="A142" s="11"/>
+      <c r="A142" s="10"/>
       <c r="C142" s="5"/>
     </row>
     <row r="143" spans="1:3">
-      <c r="A143" s="11"/>
+      <c r="A143" s="10"/>
       <c r="C143" s="5"/>
     </row>
     <row r="144" spans="1:3">
-      <c r="A144" s="11"/>
+      <c r="A144" s="10"/>
       <c r="C144" s="5"/>
     </row>
     <row r="145" spans="1:3">
-      <c r="A145" s="11"/>
+      <c r="A145" s="10"/>
       <c r="C145" s="5"/>
     </row>
     <row r="146" spans="1:3">
-      <c r="A146" s="11"/>
+      <c r="A146" s="10"/>
       <c r="C146" s="5"/>
     </row>
     <row r="147" spans="1:3">
-      <c r="A147" s="11"/>
+      <c r="A147" s="10"/>
       <c r="C147" s="5"/>
     </row>
     <row r="148" spans="1:3">
-      <c r="A148" s="11"/>
+      <c r="A148" s="10"/>
       <c r="C148" s="5"/>
     </row>
     <row r="149" spans="1:3">
-      <c r="A149" s="11"/>
+      <c r="A149" s="10"/>
       <c r="C149" s="5"/>
     </row>
     <row r="150" spans="1:3">
-      <c r="A150" s="11"/>
+      <c r="A150" s="10"/>
       <c r="C150" s="5"/>
     </row>
     <row r="151" spans="1:3">
-      <c r="A151" s="11"/>
+      <c r="A151" s="10"/>
       <c r="C151" s="5"/>
     </row>
     <row r="152" spans="1:3">
-      <c r="A152" s="11"/>
+      <c r="A152" s="10"/>
       <c r="C152" s="5"/>
     </row>
     <row r="153" spans="1:3">
-      <c r="A153" s="11"/>
+      <c r="A153" s="10"/>
       <c r="C153" s="5"/>
     </row>
     <row r="154" spans="1:3">
-      <c r="A154" s="11"/>
+      <c r="A154" s="10"/>
       <c r="C154" s="5"/>
     </row>
     <row r="155" spans="1:3">
-      <c r="A155" s="11"/>
+      <c r="A155" s="10"/>
       <c r="C155" s="5"/>
     </row>
     <row r="156" spans="1:3">
-      <c r="A156" s="11"/>
+      <c r="A156" s="10"/>
       <c r="C156" s="5"/>
     </row>
     <row r="157" spans="1:3">
-      <c r="A157" s="11"/>
+      <c r="A157" s="10"/>
       <c r="C157" s="5"/>
     </row>
     <row r="158" spans="1:3">
-      <c r="A158" s="11"/>
+      <c r="A158" s="10"/>
       <c r="C158" s="5"/>
     </row>
     <row r="159" spans="1:3">
-      <c r="A159" s="11"/>
+      <c r="A159" s="10"/>
       <c r="C159" s="5"/>
     </row>
     <row r="160" spans="1:3">
-      <c r="A160" s="11"/>
+      <c r="A160" s="10"/>
       <c r="C160" s="5"/>
     </row>
     <row r="161" spans="1:3">
-      <c r="A161" s="11"/>
+      <c r="A161" s="10"/>
       <c r="C161" s="5"/>
     </row>
     <row r="162" spans="1:3">
-      <c r="A162" s="11"/>
+      <c r="A162" s="10"/>
       <c r="C162" s="5"/>
     </row>
     <row r="163" spans="1:3">
-      <c r="A163" s="11"/>
+      <c r="A163" s="10"/>
       <c r="C163" s="5"/>
     </row>
     <row r="164" spans="1:3">
-      <c r="A164" s="11"/>
+      <c r="A164" s="10"/>
       <c r="C164" s="5"/>
     </row>
     <row r="165" spans="1:3">
-      <c r="A165" s="11"/>
+      <c r="A165" s="10"/>
       <c r="C165" s="5"/>
     </row>
     <row r="166" spans="1:3">
-      <c r="A166" s="11"/>
+      <c r="A166" s="10"/>
       <c r="C166" s="5"/>
     </row>
     <row r="167" spans="1:3">
-      <c r="A167" s="11"/>
+      <c r="A167" s="10"/>
       <c r="C167" s="5"/>
     </row>
     <row r="168" spans="1:3">
-      <c r="A168" s="11"/>
+      <c r="A168" s="10"/>
       <c r="C168" s="5"/>
     </row>
     <row r="169" spans="1:3">
-      <c r="A169" s="11"/>
+      <c r="A169" s="10"/>
       <c r="C169" s="5"/>
     </row>
     <row r="170" spans="1:3">
-      <c r="A170" s="11"/>
+      <c r="A170" s="10"/>
       <c r="C170" s="5"/>
     </row>
     <row r="171" spans="1:3">
-      <c r="A171" s="11"/>
+      <c r="A171" s="10"/>
       <c r="C171" s="5"/>
     </row>
     <row r="172" spans="1:3">
-      <c r="A172" s="11"/>
+      <c r="A172" s="10"/>
       <c r="C172" s="5"/>
     </row>
     <row r="173" spans="1:3">
-      <c r="A173" s="11"/>
+      <c r="A173" s="10"/>
       <c r="C173" s="5"/>
     </row>
     <row r="174" spans="1:3">
-      <c r="A174" s="11"/>
+      <c r="A174" s="10"/>
       <c r="C174" s="5"/>
     </row>
     <row r="175" spans="1:3">
-      <c r="A175" s="11"/>
+      <c r="A175" s="10"/>
       <c r="C175" s="5"/>
     </row>
     <row r="176" spans="1:3">
-      <c r="A176" s="11"/>
+      <c r="A176" s="10"/>
       <c r="C176" s="5"/>
     </row>
     <row r="177" spans="1:3">
-      <c r="A177" s="11"/>
+      <c r="A177" s="10"/>
       <c r="C177" s="5"/>
     </row>
     <row r="178" spans="1:3">
-      <c r="A178" s="11"/>
+      <c r="A178" s="10"/>
       <c r="C178" s="5"/>
     </row>
     <row r="179" spans="1:3">
-      <c r="A179" s="11"/>
+      <c r="A179" s="10"/>
       <c r="C179" s="5"/>
     </row>
     <row r="180" spans="1:3">
-      <c r="A180" s="11"/>
+      <c r="A180" s="10"/>
       <c r="C180" s="5"/>
     </row>
     <row r="181" spans="1:3">
-      <c r="A181" s="11"/>
+      <c r="A181" s="10"/>
       <c r="C181" s="5"/>
     </row>
     <row r="182" spans="1:3">
-      <c r="A182" s="11"/>
+      <c r="A182" s="10"/>
       <c r="C182" s="5"/>
     </row>
     <row r="183" spans="1:3">
-      <c r="A183" s="11"/>
+      <c r="A183" s="10"/>
       <c r="C183" s="5"/>
     </row>
     <row r="184" spans="1:3">
-      <c r="A184" s="11"/>
+      <c r="A184" s="10"/>
       <c r="C184" s="5"/>
     </row>
     <row r="185" spans="1:3">
-      <c r="A185" s="11"/>
+      <c r="A185" s="10"/>
       <c r="C185" s="5"/>
     </row>
     <row r="186" spans="1:3">
-      <c r="A186" s="11"/>
+      <c r="A186" s="10"/>
       <c r="C186" s="5"/>
     </row>
     <row r="187" spans="1:3">
-      <c r="A187" s="11"/>
+      <c r="A187" s="10"/>
       <c r="C187" s="5"/>
     </row>
     <row r="188" spans="1:3">
-      <c r="A188" s="11"/>
+      <c r="A188" s="10"/>
       <c r="C188" s="5"/>
     </row>
     <row r="189" spans="1:3">
-      <c r="A189" s="11"/>
+      <c r="A189" s="10"/>
       <c r="C189" s="5"/>
     </row>
     <row r="190" spans="1:3">
-      <c r="A190" s="11"/>
+      <c r="A190" s="10"/>
       <c r="C190" s="5"/>
     </row>
     <row r="191" spans="1:3">
-      <c r="A191" s="11"/>
+      <c r="A191" s="10"/>
       <c r="C191" s="5"/>
     </row>
     <row r="192" spans="1:3">
-      <c r="A192" s="11"/>
+      <c r="A192" s="10"/>
       <c r="C192" s="5"/>
     </row>
     <row r="193" spans="1:3">
-      <c r="A193" s="11"/>
+      <c r="A193" s="10"/>
       <c r="C193" s="5"/>
     </row>
   </sheetData>

--- a/hall/resources/sample/WealthRouletteReward.xlsx
+++ b/hall/resources/sample/WealthRouletteReward.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="33">
   <si>
     <t>ID</t>
   </si>
@@ -73,73 +73,61 @@
     <t>金币</t>
   </si>
   <si>
-    <t>1990000_2000</t>
+    <t>1990000_5000</t>
   </si>
   <si>
     <t>cflp_zjm_icon_2.png</t>
   </si>
   <si>
-    <t>1990000_5000</t>
+    <t>1990000_6000</t>
+  </si>
+  <si>
+    <t>1990000_7000</t>
+  </si>
+  <si>
+    <t>1990000_8000</t>
+  </si>
+  <si>
+    <t>1990000_9000</t>
   </si>
   <si>
     <t>1990000_10000</t>
   </si>
   <si>
+    <t>1990000_15000</t>
+  </si>
+  <si>
+    <t>cflp_zjm_icon_3.png</t>
+  </si>
+  <si>
     <t>1990000_20000</t>
   </si>
   <si>
+    <t>1990000_30000</t>
+  </si>
+  <si>
+    <t>1990000_40000</t>
+  </si>
+  <si>
     <t>1990000_50000</t>
   </si>
   <si>
+    <t>1990000_60000</t>
+  </si>
+  <si>
+    <t>1990000_70000</t>
+  </si>
+  <si>
     <t>1990000_80000</t>
   </si>
   <si>
     <t>1990000_100000</t>
   </si>
   <si>
-    <t>cflp_zjm_icon_3.png</t>
-  </si>
-  <si>
-    <t>1990000_150000</t>
+    <t>cflp_zjm_icon_4.png</t>
   </si>
   <si>
     <t>1990000_200000</t>
-  </si>
-  <si>
-    <t>1990000_300000</t>
-  </si>
-  <si>
-    <t>1990000_500000</t>
-  </si>
-  <si>
-    <t>1990000_800000</t>
-  </si>
-  <si>
-    <t>1990000_1000000</t>
-  </si>
-  <si>
-    <t>1990000_1500000</t>
-  </si>
-  <si>
-    <t>cflp_zjm_icon_4.png</t>
-  </si>
-  <si>
-    <t>1990000_2000000</t>
-  </si>
-  <si>
-    <t>1990000_2500000</t>
-  </si>
-  <si>
-    <t>1990000_5000000</t>
-  </si>
-  <si>
-    <t>1990000_8000000</t>
-  </si>
-  <si>
-    <t>1990000_10000000</t>
-  </si>
-  <si>
-    <t>1990000_20000000</t>
   </si>
 </sst>
 </file>
@@ -1112,7 +1100,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O193"/>
+  <dimension ref="A1:O189"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="12.875" style="1" customWidth="1"/>
@@ -1196,11 +1184,11 @@
         <v>14</v>
       </c>
       <c r="D5" s="8">
-        <v>1300</v>
+        <v>1873</v>
       </c>
       <c r="E5" s="9">
         <f>D5/10000</f>
-        <v>0.13</v>
+        <v>0.1873</v>
       </c>
       <c r="F5" t="s">
         <v>15</v>
@@ -1219,11 +1207,11 @@
         <v>16</v>
       </c>
       <c r="D6" s="8">
-        <v>1400</v>
+        <v>1873</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" ref="E6:E24" si="0">D6/10000</f>
-        <v>0.14</v>
+        <v>0.1873</v>
       </c>
       <c r="F6" t="s">
         <v>15</v>
@@ -1242,11 +1230,11 @@
         <v>17</v>
       </c>
       <c r="D7" s="8">
-        <v>1500</v>
+        <v>2060</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
-        <v>0.15</v>
+        <v>0.206</v>
       </c>
       <c r="F7" t="s">
         <v>15</v>
@@ -1265,11 +1253,11 @@
         <v>18</v>
       </c>
       <c r="D8" s="8">
-        <v>1200</v>
+        <v>2247</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0.2247</v>
       </c>
       <c r="F8" t="s">
         <v>15</v>
@@ -1288,11 +1276,11 @@
         <v>19</v>
       </c>
       <c r="D9" s="8">
-        <v>1050</v>
+        <v>375</v>
       </c>
       <c r="E9" s="9">
         <f t="shared" si="0"/>
-        <v>0.105</v>
+        <v>0.0375</v>
       </c>
       <c r="F9" t="s">
         <v>15</v>
@@ -1311,11 +1299,11 @@
         <v>20</v>
       </c>
       <c r="D10" s="8">
-        <v>1000</v>
+        <v>375</v>
       </c>
       <c r="E10" s="9">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.0375</v>
       </c>
       <c r="F10" t="s">
         <v>15</v>
@@ -1334,11 +1322,11 @@
         <v>21</v>
       </c>
       <c r="D11" s="8">
-        <v>1000</v>
+        <v>375</v>
       </c>
       <c r="E11" s="9">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.0375</v>
       </c>
       <c r="F11" t="s">
         <v>22</v>
@@ -1357,11 +1345,11 @@
         <v>23</v>
       </c>
       <c r="D12" s="8">
-        <v>1030</v>
+        <v>187</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="0"/>
-        <v>0.103</v>
+        <v>0.0187</v>
       </c>
       <c r="F12" t="s">
         <v>22</v>
@@ -1380,11 +1368,11 @@
         <v>24</v>
       </c>
       <c r="D13" s="8">
-        <v>100</v>
+        <v>187</v>
       </c>
       <c r="E13" s="9">
         <f t="shared" si="0"/>
-        <v>0.01</v>
+        <v>0.0187</v>
       </c>
       <c r="F13" t="s">
         <v>22</v>
@@ -1403,11 +1391,11 @@
         <v>25</v>
       </c>
       <c r="D14" s="8">
-        <v>100</v>
+        <v>187</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="0"/>
-        <v>0.01</v>
+        <v>0.0187</v>
       </c>
       <c r="F14" t="s">
         <v>22</v>
@@ -1426,11 +1414,11 @@
         <v>26</v>
       </c>
       <c r="D15" s="8">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="0"/>
-        <v>0.01</v>
+        <v>0.0075</v>
       </c>
       <c r="F15" t="s">
         <v>22</v>
@@ -1449,11 +1437,11 @@
         <v>27</v>
       </c>
       <c r="D16" s="8">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E16" s="9">
         <f t="shared" si="0"/>
-        <v>0.005</v>
+        <v>0.0075</v>
       </c>
       <c r="F16" t="s">
         <v>22</v>
@@ -1472,11 +1460,11 @@
         <v>28</v>
       </c>
       <c r="D17" s="8">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E17" s="9">
         <f t="shared" si="0"/>
-        <v>0.005</v>
+        <v>0.0075</v>
       </c>
       <c r="F17" t="s">
         <v>22</v>
@@ -1495,14 +1483,14 @@
         <v>29</v>
       </c>
       <c r="D18" s="8">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="E18" s="9">
         <f t="shared" si="0"/>
-        <v>0.005</v>
+        <v>0.0019</v>
       </c>
       <c r="F18" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
@@ -1515,17 +1503,17 @@
         <v>13</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" s="8">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E19" s="9">
         <f t="shared" si="0"/>
-        <v>0.002</v>
+        <v>0.0011</v>
       </c>
       <c r="F19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
@@ -1541,110 +1529,39 @@
         <v>32</v>
       </c>
       <c r="D20" s="8">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E20" s="9">
         <f t="shared" si="0"/>
-        <v>0.002</v>
+        <v>0.0007</v>
       </c>
       <c r="F20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="7">
-        <v>17</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" s="8">
-        <v>20</v>
-      </c>
-      <c r="E21" s="9">
-        <f t="shared" si="0"/>
-        <v>0.002</v>
-      </c>
-      <c r="F21" t="s">
-        <v>30</v>
-      </c>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-    </row>
-    <row r="22" spans="1:15">
-      <c r="A22" s="7">
-        <v>18</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="8">
-        <v>5</v>
-      </c>
-      <c r="E22" s="9">
-        <f t="shared" si="0"/>
-        <v>0.0005</v>
-      </c>
-      <c r="F22" t="s">
-        <v>30</v>
-      </c>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-    </row>
-    <row r="23" spans="1:15">
-      <c r="A23" s="7">
-        <v>19</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D23" s="8">
-        <v>3</v>
-      </c>
-      <c r="E23" s="9">
-        <f t="shared" si="0"/>
-        <v>0.0003</v>
-      </c>
-      <c r="F23" t="s">
-        <v>30</v>
-      </c>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-    </row>
-    <row r="24" spans="1:15">
-      <c r="A24" s="7">
-        <v>20</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D24" s="8">
-        <v>2</v>
-      </c>
-      <c r="E24" s="9">
-        <f t="shared" si="0"/>
-        <v>0.0002</v>
-      </c>
-      <c r="F24" t="s">
-        <v>30</v>
-      </c>
-      <c r="O24" s="5"/>
-    </row>
-    <row r="25" spans="1:15">
+      <c r="A21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="5"/>
+    </row>
+    <row r="22" customFormat="1" spans="1:15">
+      <c r="A22" s="10"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="5"/>
+    </row>
+    <row r="23" customFormat="1" spans="1:15">
+      <c r="A23" s="10"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="5"/>
+    </row>
+    <row r="24" customFormat="1" spans="1:15">
+      <c r="A24" s="10"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="5"/>
+    </row>
+    <row r="25" customFormat="1" spans="1:15">
       <c r="A25" s="10"/>
       <c r="B25" s="11"/>
       <c r="C25" s="5"/>
@@ -1677,12 +1594,10 @@
     <row r="31" customFormat="1" spans="1:15">
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
-      <c r="C31" s="5"/>
     </row>
     <row r="32" customFormat="1" spans="1:15">
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
-      <c r="C32" s="5"/>
     </row>
     <row r="33" customFormat="1" spans="1:3">
       <c r="A33" s="10"/>
@@ -1697,6 +1612,7 @@
     <row r="35" customFormat="1" spans="1:3">
       <c r="A35" s="10"/>
       <c r="B35" s="11"/>
+      <c r="C35" s="5"/>
     </row>
     <row r="36" customFormat="1" spans="1:3">
       <c r="A36" s="10"/>
@@ -1710,7 +1626,6 @@
     <row r="38" customFormat="1" spans="1:3">
       <c r="A38" s="10"/>
       <c r="B38" s="11"/>
-      <c r="C38" s="5"/>
     </row>
     <row r="39" customFormat="1" spans="1:3">
       <c r="A39" s="10"/>
@@ -1720,6 +1635,7 @@
     <row r="40" customFormat="1" spans="1:3">
       <c r="A40" s="10"/>
       <c r="B40" s="11"/>
+      <c r="C40" s="5"/>
     </row>
     <row r="41" customFormat="1" spans="1:3">
       <c r="A41" s="10"/>
@@ -1729,6 +1645,7 @@
     <row r="42" customFormat="1" spans="1:3">
       <c r="A42" s="10"/>
       <c r="B42" s="11"/>
+      <c r="C42" s="5"/>
     </row>
     <row r="43" customFormat="1" spans="1:3">
       <c r="A43" s="10"/>
@@ -1745,22 +1662,22 @@
       <c r="B45" s="11"/>
       <c r="C45" s="5"/>
     </row>
-    <row r="46" customFormat="1" spans="1:3">
+    <row r="46" spans="1:3">
       <c r="A46" s="10"/>
       <c r="B46" s="11"/>
       <c r="C46" s="5"/>
     </row>
-    <row r="47" customFormat="1" spans="1:3">
+    <row r="47" spans="1:3">
       <c r="A47" s="10"/>
       <c r="B47" s="11"/>
       <c r="C47" s="5"/>
     </row>
-    <row r="48" customFormat="1" spans="1:3">
+    <row r="48" spans="1:3">
       <c r="A48" s="10"/>
       <c r="B48" s="11"/>
       <c r="C48" s="5"/>
     </row>
-    <row r="49" customFormat="1" spans="1:3">
+    <row r="49" spans="1:3">
       <c r="A49" s="10"/>
       <c r="B49" s="11"/>
       <c r="C49" s="5"/>
@@ -1987,22 +1904,22 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="10"/>
-      <c r="B94" s="11"/>
+      <c r="B94" s="12"/>
       <c r="C94" s="5"/>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="10"/>
-      <c r="B95" s="11"/>
+      <c r="B95" s="12"/>
       <c r="C95" s="5"/>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="10"/>
-      <c r="B96" s="11"/>
+      <c r="B96" s="12"/>
       <c r="C96" s="5"/>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="10"/>
-      <c r="B97" s="11"/>
+      <c r="B97" s="12"/>
       <c r="C97" s="5"/>
     </row>
     <row r="98" spans="1:3">
@@ -2047,22 +1964,18 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="10"/>
-      <c r="B106" s="12"/>
       <c r="C106" s="5"/>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="10"/>
-      <c r="B107" s="12"/>
       <c r="C107" s="5"/>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" s="10"/>
-      <c r="B108" s="12"/>
       <c r="C108" s="5"/>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="10"/>
-      <c r="B109" s="12"/>
       <c r="C109" s="5"/>
     </row>
     <row r="110" spans="1:3">
@@ -2384,22 +2297,6 @@
     <row r="189" spans="1:3">
       <c r="A189" s="10"/>
       <c r="C189" s="5"/>
-    </row>
-    <row r="190" spans="1:3">
-      <c r="A190" s="10"/>
-      <c r="C190" s="5"/>
-    </row>
-    <row r="191" spans="1:3">
-      <c r="A191" s="10"/>
-      <c r="C191" s="5"/>
-    </row>
-    <row r="192" spans="1:3">
-      <c r="A192" s="10"/>
-      <c r="C192" s="5"/>
-    </row>
-    <row r="193" spans="1:3">
-      <c r="A193" s="10"/>
-      <c r="C193" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/WealthRouletteReward.xlsx
+++ b/hall/resources/sample/WealthRouletteReward.xlsx
@@ -73,61 +73,61 @@
     <t>金币</t>
   </si>
   <si>
+    <t>1990000_200000</t>
+  </si>
+  <si>
+    <t>cflp_zjm_icon_4.png</t>
+  </si>
+  <si>
+    <t>1990000_150000</t>
+  </si>
+  <si>
+    <t>1990000_100000</t>
+  </si>
+  <si>
+    <t>1990000_80000</t>
+  </si>
+  <si>
+    <t>1990000_50000</t>
+  </si>
+  <si>
+    <t>1990000_20000</t>
+  </si>
+  <si>
+    <t>cflp_zjm_icon_3.png</t>
+  </si>
+  <si>
+    <t>1990000_10000</t>
+  </si>
+  <si>
+    <t>1990000_9000</t>
+  </si>
+  <si>
+    <t>1990000_8000</t>
+  </si>
+  <si>
+    <t>1990000_7000</t>
+  </si>
+  <si>
+    <t>1990000_6000</t>
+  </si>
+  <si>
     <t>1990000_5000</t>
   </si>
   <si>
     <t>cflp_zjm_icon_2.png</t>
   </si>
   <si>
-    <t>1990000_6000</t>
-  </si>
-  <si>
-    <t>1990000_7000</t>
-  </si>
-  <si>
-    <t>1990000_8000</t>
-  </si>
-  <si>
-    <t>1990000_9000</t>
-  </si>
-  <si>
-    <t>1990000_10000</t>
-  </si>
-  <si>
-    <t>1990000_15000</t>
-  </si>
-  <si>
-    <t>cflp_zjm_icon_3.png</t>
-  </si>
-  <si>
-    <t>1990000_20000</t>
-  </si>
-  <si>
-    <t>1990000_30000</t>
-  </si>
-  <si>
-    <t>1990000_40000</t>
-  </si>
-  <si>
-    <t>1990000_50000</t>
-  </si>
-  <si>
-    <t>1990000_60000</t>
-  </si>
-  <si>
-    <t>1990000_70000</t>
-  </si>
-  <si>
-    <t>1990000_80000</t>
-  </si>
-  <si>
-    <t>1990000_100000</t>
-  </si>
-  <si>
-    <t>cflp_zjm_icon_4.png</t>
-  </si>
-  <si>
-    <t>1990000_200000</t>
+    <t>1990000_4000</t>
+  </si>
+  <si>
+    <t>1990000_3000</t>
+  </si>
+  <si>
+    <t>1990000_2000</t>
+  </si>
+  <si>
+    <t>1990000_1000</t>
   </si>
 </sst>
 </file>
@@ -1184,11 +1184,10 @@
         <v>14</v>
       </c>
       <c r="D5" s="8">
-        <v>1873</v>
+        <v>4</v>
       </c>
       <c r="E5" s="9">
-        <f>D5/10000</f>
-        <v>0.1873</v>
+        <v>0.0004</v>
       </c>
       <c r="F5" t="s">
         <v>15</v>
@@ -1207,11 +1206,10 @@
         <v>16</v>
       </c>
       <c r="D6" s="8">
-        <v>1873</v>
+        <v>11</v>
       </c>
       <c r="E6" s="9">
-        <f t="shared" ref="E6:E24" si="0">D6/10000</f>
-        <v>0.1873</v>
+        <v>0.0011</v>
       </c>
       <c r="F6" t="s">
         <v>15</v>
@@ -1230,11 +1228,10 @@
         <v>17</v>
       </c>
       <c r="D7" s="8">
-        <v>2060</v>
+        <v>18</v>
       </c>
       <c r="E7" s="9">
-        <f t="shared" si="0"/>
-        <v>0.206</v>
+        <v>0.0018</v>
       </c>
       <c r="F7" t="s">
         <v>15</v>
@@ -1253,11 +1250,10 @@
         <v>18</v>
       </c>
       <c r="D8" s="8">
-        <v>2247</v>
+        <v>54</v>
       </c>
       <c r="E8" s="9">
-        <f t="shared" si="0"/>
-        <v>0.2247</v>
+        <v>0.0054</v>
       </c>
       <c r="F8" t="s">
         <v>15</v>
@@ -1276,11 +1272,10 @@
         <v>19</v>
       </c>
       <c r="D9" s="8">
-        <v>375</v>
+        <v>72</v>
       </c>
       <c r="E9" s="9">
-        <f t="shared" si="0"/>
-        <v>0.0375</v>
+        <v>0.0072</v>
       </c>
       <c r="F9" t="s">
         <v>15</v>
@@ -1299,14 +1294,13 @@
         <v>20</v>
       </c>
       <c r="D10" s="8">
-        <v>375</v>
+        <v>90</v>
       </c>
       <c r="E10" s="9">
-        <f t="shared" si="0"/>
-        <v>0.0375</v>
+        <v>0.009</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
@@ -1319,17 +1313,16 @@
         <v>13</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="8">
+        <v>361</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0.0361</v>
+      </c>
+      <c r="F11" t="s">
         <v>21</v>
-      </c>
-      <c r="D11" s="8">
-        <v>375</v>
-      </c>
-      <c r="E11" s="9">
-        <f t="shared" si="0"/>
-        <v>0.0375</v>
-      </c>
-      <c r="F11" t="s">
-        <v>22</v>
       </c>
       <c r="N11" s="5"/>
       <c r="O11" s="5"/>
@@ -1345,14 +1338,13 @@
         <v>23</v>
       </c>
       <c r="D12" s="8">
-        <v>187</v>
+        <v>361</v>
       </c>
       <c r="E12" s="9">
-        <f t="shared" si="0"/>
-        <v>0.0187</v>
+        <v>0.0361</v>
       </c>
       <c r="F12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
@@ -1368,14 +1360,13 @@
         <v>24</v>
       </c>
       <c r="D13" s="8">
-        <v>187</v>
+        <v>361</v>
       </c>
       <c r="E13" s="9">
-        <f t="shared" si="0"/>
-        <v>0.0187</v>
+        <v>0.0361</v>
       </c>
       <c r="F13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
@@ -1391,14 +1382,13 @@
         <v>25</v>
       </c>
       <c r="D14" s="8">
-        <v>187</v>
+        <v>361</v>
       </c>
       <c r="E14" s="9">
-        <f t="shared" si="0"/>
-        <v>0.0187</v>
+        <v>0.0361</v>
       </c>
       <c r="F14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
@@ -1414,14 +1404,13 @@
         <v>26</v>
       </c>
       <c r="D15" s="8">
-        <v>75</v>
+        <v>361</v>
       </c>
       <c r="E15" s="9">
-        <f t="shared" si="0"/>
-        <v>0.0075</v>
+        <v>0.0361</v>
       </c>
       <c r="F15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
@@ -1437,14 +1426,13 @@
         <v>27</v>
       </c>
       <c r="D16" s="8">
-        <v>75</v>
+        <v>722</v>
       </c>
       <c r="E16" s="9">
-        <f t="shared" si="0"/>
-        <v>0.0075</v>
+        <v>0.0722</v>
       </c>
       <c r="F16" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
@@ -1457,17 +1445,16 @@
         <v>13</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="8">
+        <v>1806</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0.1806</v>
+      </c>
+      <c r="F17" t="s">
         <v>28</v>
-      </c>
-      <c r="D17" s="8">
-        <v>75</v>
-      </c>
-      <c r="E17" s="9">
-        <f t="shared" si="0"/>
-        <v>0.0075</v>
-      </c>
-      <c r="F17" t="s">
-        <v>22</v>
       </c>
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
@@ -1480,17 +1467,16 @@
         <v>13</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" s="8">
-        <v>19</v>
+        <v>1806</v>
       </c>
       <c r="E18" s="9">
-        <f t="shared" si="0"/>
-        <v>0.0019</v>
+        <v>0.1806</v>
       </c>
       <c r="F18" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
@@ -1503,17 +1489,16 @@
         <v>13</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" s="8">
-        <v>11</v>
+        <v>1806</v>
       </c>
       <c r="E19" s="9">
-        <f t="shared" si="0"/>
-        <v>0.0011</v>
+        <v>0.1806</v>
       </c>
       <c r="F19" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
@@ -1529,14 +1514,13 @@
         <v>32</v>
       </c>
       <c r="D20" s="8">
-        <v>7</v>
+        <v>1806</v>
       </c>
       <c r="E20" s="9">
-        <f t="shared" si="0"/>
-        <v>0.0007</v>
+        <v>0.1806</v>
       </c>
       <c r="F20" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>

--- a/hall/resources/sample/WealthRouletteReward.xlsx
+++ b/hall/resources/sample/WealthRouletteReward.xlsx
@@ -1187,7 +1187,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="9">
-        <v>0.0004</v>
+        <v>0.0004000400040004</v>
       </c>
       <c r="F5" t="s">
         <v>15</v>
@@ -1206,10 +1206,10 @@
         <v>16</v>
       </c>
       <c r="D6" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E6" s="9">
-        <v>0.0011</v>
+        <v>0.0007000700070007</v>
       </c>
       <c r="F6" t="s">
         <v>15</v>
@@ -1228,10 +1228,10 @@
         <v>17</v>
       </c>
       <c r="D7" s="8">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E7" s="9">
-        <v>0.0018</v>
+        <v>0.0011001100110011</v>
       </c>
       <c r="F7" t="s">
         <v>15</v>
@@ -1250,10 +1250,10 @@
         <v>18</v>
       </c>
       <c r="D8" s="8">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="E8" s="9">
-        <v>0.0054</v>
+        <v>0.0018001800180018</v>
       </c>
       <c r="F8" t="s">
         <v>15</v>
@@ -1272,10 +1272,10 @@
         <v>19</v>
       </c>
       <c r="D9" s="8">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="E9" s="9">
-        <v>0.0072</v>
+        <v>0.0036003600360036</v>
       </c>
       <c r="F9" t="s">
         <v>15</v>
@@ -1294,10 +1294,10 @@
         <v>20</v>
       </c>
       <c r="D10" s="8">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="E10" s="9">
-        <v>0.009</v>
+        <v>0.0073007300730073</v>
       </c>
       <c r="F10" t="s">
         <v>21</v>
@@ -1316,10 +1316,10 @@
         <v>22</v>
       </c>
       <c r="D11" s="8">
-        <v>361</v>
+        <v>109</v>
       </c>
       <c r="E11" s="9">
-        <v>0.0361</v>
+        <v>0.0109010901090109</v>
       </c>
       <c r="F11" t="s">
         <v>21</v>
@@ -1338,10 +1338,10 @@
         <v>23</v>
       </c>
       <c r="D12" s="8">
-        <v>361</v>
+        <v>146</v>
       </c>
       <c r="E12" s="9">
-        <v>0.0361</v>
+        <v>0.0146014601460146</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -1360,10 +1360,10 @@
         <v>24</v>
       </c>
       <c r="D13" s="8">
-        <v>361</v>
+        <v>219</v>
       </c>
       <c r="E13" s="9">
-        <v>0.0361</v>
+        <v>0.0219021902190219</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1382,10 +1382,10 @@
         <v>25</v>
       </c>
       <c r="D14" s="8">
-        <v>361</v>
+        <v>292</v>
       </c>
       <c r="E14" s="9">
-        <v>0.0361</v>
+        <v>0.0292029202920292</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -1404,10 +1404,10 @@
         <v>26</v>
       </c>
       <c r="D15" s="8">
-        <v>361</v>
+        <v>328</v>
       </c>
       <c r="E15" s="9">
-        <v>0.0361</v>
+        <v>0.0328032803280328</v>
       </c>
       <c r="F15" t="s">
         <v>21</v>
@@ -1426,10 +1426,10 @@
         <v>27</v>
       </c>
       <c r="D16" s="8">
-        <v>722</v>
+        <v>547</v>
       </c>
       <c r="E16" s="9">
-        <v>0.0722</v>
+        <v>0.0547054705470547</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -1448,10 +1448,10 @@
         <v>29</v>
       </c>
       <c r="D17" s="8">
-        <v>1806</v>
+        <v>2189</v>
       </c>
       <c r="E17" s="9">
-        <v>0.1806</v>
+        <v>0.218921892189219</v>
       </c>
       <c r="F17" t="s">
         <v>28</v>
@@ -1470,10 +1470,10 @@
         <v>30</v>
       </c>
       <c r="D18" s="8">
-        <v>1806</v>
+        <v>2189</v>
       </c>
       <c r="E18" s="9">
-        <v>0.1806</v>
+        <v>0.218921892189219</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -1492,10 +1492,10 @@
         <v>31</v>
       </c>
       <c r="D19" s="8">
-        <v>1806</v>
+        <v>2189</v>
       </c>
       <c r="E19" s="9">
-        <v>0.1806</v>
+        <v>0.218921892189219</v>
       </c>
       <c r="F19" t="s">
         <v>28</v>
@@ -1514,10 +1514,10 @@
         <v>32</v>
       </c>
       <c r="D20" s="8">
-        <v>1806</v>
+        <v>1642</v>
       </c>
       <c r="E20" s="9">
-        <v>0.1806</v>
+        <v>0.164216421642164</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>

--- a/hall/resources/sample/WealthRouletteReward.xlsx
+++ b/hall/resources/sample/WealthRouletteReward.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="WealthRouletteReward" sheetId="1" r:id="rId1"/>
@@ -1184,10 +1184,10 @@
         <v>14</v>
       </c>
       <c r="D5" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" s="9">
-        <v>0.0004000400040004</v>
+        <v>0.000500150045013504</v>
       </c>
       <c r="F5" t="s">
         <v>15</v>
@@ -1206,10 +1206,10 @@
         <v>16</v>
       </c>
       <c r="D6" s="8">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E6" s="9">
-        <v>0.0007000700070007</v>
+        <v>0.00110033009902971</v>
       </c>
       <c r="F6" t="s">
         <v>15</v>
@@ -1228,10 +1228,10 @@
         <v>17</v>
       </c>
       <c r="D7" s="8">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E7" s="9">
-        <v>0.0011001100110011</v>
+        <v>0.00160048014404321</v>
       </c>
       <c r="F7" t="s">
         <v>15</v>
@@ -1250,10 +1250,10 @@
         <v>18</v>
       </c>
       <c r="D8" s="8">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E8" s="9">
-        <v>0.0018001800180018</v>
+        <v>0.00270081024307292</v>
       </c>
       <c r="F8" t="s">
         <v>15</v>
@@ -1272,10 +1272,10 @@
         <v>19</v>
       </c>
       <c r="D9" s="8">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E9" s="9">
-        <v>0.0036003600360036</v>
+        <v>0.00550165049514854</v>
       </c>
       <c r="F9" t="s">
         <v>15</v>
@@ -1294,10 +1294,10 @@
         <v>20</v>
       </c>
       <c r="D10" s="8">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="E10" s="9">
-        <v>0.0073007300730073</v>
+        <v>0.0110033009902971</v>
       </c>
       <c r="F10" t="s">
         <v>21</v>
@@ -1316,10 +1316,10 @@
         <v>22</v>
       </c>
       <c r="D11" s="8">
-        <v>109</v>
+        <v>164</v>
       </c>
       <c r="E11" s="9">
-        <v>0.0109010901090109</v>
+        <v>0.0164049214764429</v>
       </c>
       <c r="F11" t="s">
         <v>21</v>
@@ -1338,10 +1338,10 @@
         <v>23</v>
       </c>
       <c r="D12" s="8">
-        <v>146</v>
+        <v>219</v>
       </c>
       <c r="E12" s="9">
-        <v>0.0146014601460146</v>
+        <v>0.0219065719715915</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -1360,10 +1360,10 @@
         <v>24</v>
       </c>
       <c r="D13" s="8">
-        <v>219</v>
+        <v>329</v>
       </c>
       <c r="E13" s="9">
-        <v>0.0219021902190219</v>
+        <v>0.0329098729618886</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1382,10 +1382,10 @@
         <v>25</v>
       </c>
       <c r="D14" s="8">
-        <v>292</v>
+        <v>439</v>
       </c>
       <c r="E14" s="9">
-        <v>0.0292029202920292</v>
+        <v>0.0439131739521857</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -1404,10 +1404,10 @@
         <v>26</v>
       </c>
       <c r="D15" s="8">
-        <v>328</v>
+        <v>548</v>
       </c>
       <c r="E15" s="9">
-        <v>0.0328032803280328</v>
+        <v>0.05481644493348</v>
       </c>
       <c r="F15" t="s">
         <v>21</v>
@@ -1426,10 +1426,10 @@
         <v>27</v>
       </c>
       <c r="D16" s="8">
-        <v>547</v>
+        <v>822</v>
       </c>
       <c r="E16" s="9">
-        <v>0.0547054705470547</v>
+        <v>0.0822246674002201</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -1448,10 +1448,10 @@
         <v>29</v>
       </c>
       <c r="D17" s="8">
-        <v>2189</v>
+        <v>3289</v>
       </c>
       <c r="E17" s="9">
-        <v>0.218921892189219</v>
+        <v>0.328998699609883</v>
       </c>
       <c r="F17" t="s">
         <v>28</v>
@@ -1470,10 +1470,10 @@
         <v>30</v>
       </c>
       <c r="D18" s="8">
-        <v>2189</v>
+        <v>1771</v>
       </c>
       <c r="E18" s="9">
-        <v>0.218921892189219</v>
+        <v>0.177153145943783</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -1492,10 +1492,10 @@
         <v>31</v>
       </c>
       <c r="D19" s="8">
-        <v>2189</v>
+        <v>1096</v>
       </c>
       <c r="E19" s="9">
-        <v>0.218921892189219</v>
+        <v>0.10963288986696</v>
       </c>
       <c r="F19" t="s">
         <v>28</v>
@@ -1514,10 +1514,10 @@
         <v>32</v>
       </c>
       <c r="D20" s="8">
-        <v>1642</v>
+        <v>1096</v>
       </c>
       <c r="E20" s="9">
-        <v>0.164216421642164</v>
+        <v>0.10963288986696</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>

--- a/hall/resources/sample/WealthRouletteReward.xlsx
+++ b/hall/resources/sample/WealthRouletteReward.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="WealthRouletteReward" sheetId="1" r:id="rId1"/>
@@ -1184,10 +1184,10 @@
         <v>14</v>
       </c>
       <c r="D5" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" s="9">
-        <v>0.000500150045013504</v>
+        <v>0.0004000400040004</v>
       </c>
       <c r="F5" t="s">
         <v>15</v>
@@ -1206,10 +1206,10 @@
         <v>16</v>
       </c>
       <c r="D6" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E6" s="9">
-        <v>0.00110033009902971</v>
+        <v>0.0007000700070007</v>
       </c>
       <c r="F6" t="s">
         <v>15</v>
@@ -1228,10 +1228,10 @@
         <v>17</v>
       </c>
       <c r="D7" s="8">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E7" s="9">
-        <v>0.00160048014404321</v>
+        <v>0.0011001100110011</v>
       </c>
       <c r="F7" t="s">
         <v>15</v>
@@ -1250,10 +1250,10 @@
         <v>18</v>
       </c>
       <c r="D8" s="8">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E8" s="9">
-        <v>0.00270081024307292</v>
+        <v>0.0018001800180018</v>
       </c>
       <c r="F8" t="s">
         <v>15</v>
@@ -1272,10 +1272,10 @@
         <v>19</v>
       </c>
       <c r="D9" s="8">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="E9" s="9">
-        <v>0.00550165049514854</v>
+        <v>0.0036003600360036</v>
       </c>
       <c r="F9" t="s">
         <v>15</v>
@@ -1294,10 +1294,10 @@
         <v>20</v>
       </c>
       <c r="D10" s="8">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="E10" s="9">
-        <v>0.0110033009902971</v>
+        <v>0.0073007300730073</v>
       </c>
       <c r="F10" t="s">
         <v>21</v>
@@ -1316,10 +1316,10 @@
         <v>22</v>
       </c>
       <c r="D11" s="8">
-        <v>164</v>
+        <v>109</v>
       </c>
       <c r="E11" s="9">
-        <v>0.0164049214764429</v>
+        <v>0.0109010901090109</v>
       </c>
       <c r="F11" t="s">
         <v>21</v>
@@ -1338,10 +1338,10 @@
         <v>23</v>
       </c>
       <c r="D12" s="8">
-        <v>219</v>
+        <v>146</v>
       </c>
       <c r="E12" s="9">
-        <v>0.0219065719715915</v>
+        <v>0.0146014601460146</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -1360,10 +1360,10 @@
         <v>24</v>
       </c>
       <c r="D13" s="8">
-        <v>329</v>
+        <v>219</v>
       </c>
       <c r="E13" s="9">
-        <v>0.0329098729618886</v>
+        <v>0.0219021902190219</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1382,10 +1382,10 @@
         <v>25</v>
       </c>
       <c r="D14" s="8">
-        <v>439</v>
+        <v>292</v>
       </c>
       <c r="E14" s="9">
-        <v>0.0439131739521857</v>
+        <v>0.0292029202920292</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -1404,10 +1404,10 @@
         <v>26</v>
       </c>
       <c r="D15" s="8">
-        <v>548</v>
+        <v>328</v>
       </c>
       <c r="E15" s="9">
-        <v>0.05481644493348</v>
+        <v>0.0328032803280328</v>
       </c>
       <c r="F15" t="s">
         <v>21</v>
@@ -1426,10 +1426,10 @@
         <v>27</v>
       </c>
       <c r="D16" s="8">
-        <v>822</v>
+        <v>547</v>
       </c>
       <c r="E16" s="9">
-        <v>0.0822246674002201</v>
+        <v>0.0547054705470547</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -1448,10 +1448,10 @@
         <v>29</v>
       </c>
       <c r="D17" s="8">
-        <v>3289</v>
+        <v>2189</v>
       </c>
       <c r="E17" s="9">
-        <v>0.328998699609883</v>
+        <v>0.218921892189219</v>
       </c>
       <c r="F17" t="s">
         <v>28</v>
@@ -1470,10 +1470,10 @@
         <v>30</v>
       </c>
       <c r="D18" s="8">
-        <v>1771</v>
+        <v>2189</v>
       </c>
       <c r="E18" s="9">
-        <v>0.177153145943783</v>
+        <v>0.218921892189219</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -1492,10 +1492,10 @@
         <v>31</v>
       </c>
       <c r="D19" s="8">
-        <v>1096</v>
+        <v>2189</v>
       </c>
       <c r="E19" s="9">
-        <v>0.10963288986696</v>
+        <v>0.218921892189219</v>
       </c>
       <c r="F19" t="s">
         <v>28</v>
@@ -1514,10 +1514,10 @@
         <v>32</v>
       </c>
       <c r="D20" s="8">
-        <v>1096</v>
+        <v>1642</v>
       </c>
       <c r="E20" s="9">
-        <v>0.10963288986696</v>
+        <v>0.164216421642164</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
